--- a/data/archive/2026-10-07.xlsx
+++ b/data/archive/2026-10-07.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:25 UTC</t>
+          <t>2026-10-07 17:36 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:25 UTC</t>
+          <t>2026-10-07 17:36 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:27 UTC</t>
+          <t>2026-10-07 17:38 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:27 UTC</t>
+          <t>2026-10-07 17:38 UTC</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:27 UTC</t>
+          <t>2026-10-07 17:38 UTC</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">

--- a/data/archive/2026-10-07.xlsx
+++ b/data/archive/2026-10-07.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:36 UTC</t>
+          <t>2026-10-07 18:09 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -924,22 +924,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Zekelman</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Intern, Automation Engineer</t>
+          <t>Security Engineer Intern [Winter 2027]</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Cambridge, OH</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -954,23 +954,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>JR002792</t>
+          <t>4719593006</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://zekelman.wd12.myworkdayjobs.com/Careers/job/Cambridge-OH/Intern--Automation-Engineer_JR002792</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -985,7 +989,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:36 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1007,32 +1011,32 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer Intern [Winter 2027]</t>
+          <t>Software Engineer, Platform Access (L2)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1047,7 +1051,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>4719593006</t>
+          <t>8026211</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1057,7 +1061,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1094,12 +1098,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform Access (L2)</t>
+          <t>Software Engineer, Performance Tooling and Infrastructure New Grad</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1109,12 +1113,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1124,17 +1128,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8026211</t>
+          <t>8227399</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8227399</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1159,7 +1163,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1186,7 +1190,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Performance Tooling and Infrastructure New Grad</t>
+          <t>Software Engineer, Software Updates</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1201,7 +1205,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1211,7 +1215,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1221,7 +1225,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8227399</t>
+          <t>8230855</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1231,7 +1235,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8227399</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1246,7 +1250,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1268,12 +1272,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Updates</t>
+          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1283,17 +1287,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1308,7 +1312,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8230855</t>
+          <t>8817974002</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1318,7 +1322,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1333,7 +1337,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1355,12 +1359,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1370,7 +1374,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1385,27 +1389,23 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>8817974002</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1442,12 +1442,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+          <t>Software Engineer, Early Career (NYC)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+          <t>New York, New York, United States</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1467,28 +1467,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>8008649003</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1503,7 +1507,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,7 +1534,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (NYC)</t>
+          <t>Software Engineer, Early Career (SF)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1540,7 +1544,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>New York, New York, United States</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1565,7 +1569,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8008649003</t>
+          <t>8010617003</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1575,7 +1579,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1590,7 +1594,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1612,12 +1616,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (SF)</t>
+          <t>Software Engineer, Web3 Backend</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1627,12 +1631,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Menlo Park, CA; New York, NY</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1642,17 +1646,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8010617003</t>
+          <t>8258305</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1662,7 +1666,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1677,7 +1681,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1699,12 +1703,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Web3 Backend</t>
+          <t>Staff Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1714,12 +1718,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1729,17 +1733,17 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>8258305</t>
+          <t>8257909</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1749,7 +1753,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
+          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1764,7 +1768,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1786,12 +1790,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Cloud Infrastructure</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1801,32 +1805,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8257909</t>
+          <t>8011590003</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1836,7 +1840,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1851,7 +1855,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1873,12 +1877,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Public Sector - New Grad</t>
+          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1888,22 +1892,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1913,7 +1917,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>4736426005</t>
+          <t>8008645003</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1923,7 +1927,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1938,7 +1942,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1965,7 +1969,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Staff Software Engineer, Backend (Search)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1975,32 +1979,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8011590003</t>
+          <t>8005406003</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2010,7 +2014,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2025,7 +2029,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2047,12 +2051,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
+          <t>C++ Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2062,42 +2066,38 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Beavercreek, OH</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>8008645003</t>
+          <t>R0240412</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:11 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2134,12 +2134,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>Spring 2027 Software Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2149,38 +2149,42 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>Palo Alto, CA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Co-op</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>R0240412</t>
+          <t>5252108007</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+          <t>https://job-boards.greenhouse.io/xai/jobs/5252108007</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2195,7 +2199,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:38 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2217,12 +2221,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Backend (Search)</t>
+          <t>Summer 2027 Software Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2232,32 +2236,32 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>Palo Alto, CA</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Co-op</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>8005406003</t>
+          <t>5255111007</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2267,7 +2271,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+          <t>https://job-boards.greenhouse.io/xai/jobs/5255111007</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2282,7 +2286,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2304,57 +2308,53 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Spring 2027 Software Engineering Internship/Co-op</t>
+          <t>Product Engineering Intern</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Co-op</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5252108007</t>
+          <t>R0250655</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/xai/jobs/5252108007</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:11 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2391,57 +2391,53 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Software Engineering Internship/Co-op</t>
+          <t>Cybersecurity Engineer, Junior</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Palo Alto, CA</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Co-op</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>5255111007</t>
+          <t>R0250290</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/xai/jobs/5255111007</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2456,7 +2452,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:11 UTC</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2470,179 +2466,13 @@
         </is>
       </c>
       <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Product Engineering Intern</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Product Engineer</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>McLean, VA</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>R0250655</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07 17:38 UTC</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Cybersecurity Engineer, Junior</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Security Engineer</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>R0250290</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07 17:38 UTC</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q25"/>
+  <autoFilter ref="A1:Q23"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2674,8 +2504,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/archive/2026-10-07.xlsx
+++ b/data/archive/2026-10-07.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -667,12 +667,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Systems Software Engineer, AI and Cloud - New College Grad 2026</t>
+          <t>New Grad Software Engineer, Product Engineering</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -697,23 +697,27 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>JR2025458</t>
+          <t>8248317</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Systems-Software-Engineer---AI-and-Cloud---New-College-Grad-2026_JR2025458</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -728,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:09 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -750,12 +754,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>New Grad Software Engineer, Product Engineering</t>
+          <t>Systems Software Engineer, AI and Cloud - New College Grad 2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -780,27 +784,23 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8248317</t>
+          <t>JR2025458</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Systems-Software-Engineer---AI-and-Cloud---New-College-Grad-2026_JR2025458</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:42 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:11 UTC</t>
+          <t>2026-10-07 18:44 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:11 UTC</t>
+          <t>2026-10-07 18:44 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:11 UTC</t>
+          <t>2026-10-07 18:44 UTC</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">

--- a/data/archive/2026-10-07.xlsx
+++ b/data/archive/2026-10-07.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:42 UTC</t>
+          <t>2026-10-07 19:14 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -924,22 +924,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Zekelman</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Security Engineer Intern [Winter 2027]</t>
+          <t>Intern, Automation Engineer</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Cambridge, OH</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -954,27 +954,23 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4719593006</t>
+          <t>JR002792</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
+          <t>https://zekelman.wd12.myworkdayjobs.com/Careers/job/Cambridge-OH/Intern--Automation-Engineer_JR002792</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -989,7 +985,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:14 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,32 +1007,32 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform Access (L2)</t>
+          <t>Security Engineer Intern [Winter 2027]</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1046,12 +1042,12 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8026211</t>
+          <t>4719593006</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1061,7 +1057,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1076,7 +1072,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1098,12 +1094,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Performance Tooling and Infrastructure New Grad</t>
+          <t>Software Engineer, Platform Access (L2)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1113,12 +1109,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1128,7 +1124,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1138,7 +1134,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8227399</t>
+          <t>8026211</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1148,7 +1144,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8227399</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1163,7 +1159,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:11 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1190,7 +1186,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Updates</t>
+          <t>Software Engineer, Performance Tooling and Infrastructure New Grad</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1205,7 +1201,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1215,17 +1211,17 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8230855</t>
+          <t>8227399</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1235,7 +1231,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8227399</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1250,7 +1246,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1272,12 +1268,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Software Updates</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1287,17 +1283,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1312,7 +1308,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8817974002</t>
+          <t>8230855</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1322,7 +1318,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1337,7 +1333,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1359,12 +1355,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1374,7 +1370,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1389,23 +1385,27 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>8817974002</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1442,12 +1442,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (NYC)</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>New York, New York, United States</t>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1467,32 +1467,28 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8008649003</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1507,7 +1503,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1534,7 +1530,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (SF)</t>
+          <t>Software Engineer, Early Career (NYC)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1544,7 +1540,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>New York, New York, United States</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1569,7 +1565,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8010617003</t>
+          <t>8008649003</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1579,7 +1575,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1594,7 +1590,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1616,12 +1612,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Web3 Backend</t>
+          <t>Software Engineer, Early Career (SF)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1631,12 +1627,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1646,17 +1642,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8258305</t>
+          <t>8010617003</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1666,7 +1662,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1681,7 +1677,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1703,12 +1699,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Cloud Infrastructure</t>
+          <t>Software Engineer, Web3 Backend</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1718,12 +1714,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>Menlo Park, CA; New York, NY</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1733,17 +1729,17 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>8257909</t>
+          <t>8258305</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1753,7 +1749,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1768,7 +1764,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1790,12 +1786,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Staff Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1805,22 +1801,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1830,7 +1826,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8011590003</t>
+          <t>8257909</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1840,7 +1836,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
+          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1855,7 +1851,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:11 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1882,7 +1878,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1897,7 +1893,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1917,7 +1913,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>8008645003</t>
+          <t>8011590003</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1927,7 +1923,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1942,7 +1938,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1969,7 +1965,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Backend (Search)</t>
+          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1979,7 +1975,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1989,22 +1985,22 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8005406003</t>
+          <t>8008645003</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2014,7 +2010,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2029,7 +2025,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2051,12 +2047,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>Staff Software Engineer, Backend (Search)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2066,12 +2062,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -2081,23 +2077,27 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>R0240412</t>
+          <t>8005406003</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:44 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2134,12 +2134,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Spring 2027 Software Engineering Internship/Co-op</t>
+          <t>C++ Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2149,42 +2149,38 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA</t>
+          <t>Beavercreek, OH</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Co-op</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5252108007</t>
+          <t>R0240412</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/xai/jobs/5252108007</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2199,7 +2195,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:16 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2226,7 +2222,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Software Engineering Internship/Co-op</t>
+          <t>Spring 2027 Software Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2261,7 +2257,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>5255111007</t>
+          <t>5252108007</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2271,7 +2267,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/xai/jobs/5255111007</t>
+          <t>https://job-boards.greenhouse.io/xai/jobs/5252108007</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2286,7 +2282,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2308,53 +2304,57 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Product Engineering Intern</t>
+          <t>Summer 2027 Software Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>Palo Alto, CA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Co-op</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>R0250655</t>
+          <t>5255111007</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+          <t>https://job-boards.greenhouse.io/xai/jobs/5255111007</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:44 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer, Junior</t>
+          <t>Product Engineering Intern</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2416,63 +2416,146 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
+          <t>R0250655</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:16 UTC</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>R0250290</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07 18:44 UTC</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:16 UTC</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q23"/>
+  <autoFilter ref="A1:Q24"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2504,6 +2587,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
